--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19F34D0-A453-4053-B459-286BAE18CD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
   </bookViews>
   <sheets>
-    <sheet name="Step case and steps" sheetId="1" r:id="rId1"/>
-    <sheet name="Test data" sheetId="2" r:id="rId2"/>
-    <sheet name="Console Errors" sheetId="3" r:id="rId3"/>
-    <sheet name="Jira Tracker" sheetId="4" r:id="rId4"/>
-    <sheet name="API Test Cases" sheetId="5" r:id="rId5"/>
+    <sheet sheetId="1" name="Step case and steps" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Test data" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Console Errors" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Jira Tracker" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="API Test Cases" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Daily Shakeout" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Step case and steps'!$A$2:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase">'Step case and steps'!$A$2:$I$2</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5238" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5421" uniqueCount="722">
   <si>
     <t>Test case</t>
   </si>
@@ -1909,27 +1909,368 @@
   </si>
   <si>
     <t>PATCH /api/v1/users/me/password with valid auth and data → 200</t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Test Group</t>
+  </si>
+  <si>
+    <t>Test File</t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Env</t>
+  </si>
+  <si>
+    <t>Run for Smoketest</t>
+  </si>
+  <si>
+    <t>01-tg1-login-health.spec.ts</t>
+  </si>
+  <si>
+    <t>Login page loads — HTTP 200, no server errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /login
+2. Verify HTTP status &lt; 400
+3. Verify email input field is visible</t>
+  </si>
+  <si>
+    <t>Login page renders with email input</t>
+  </si>
+  <si>
+    <t>POC + Prod</t>
+  </si>
+  <si>
+    <t>Health endpoint — API backend is alive</t>
+  </si>
+  <si>
+    <t>1. GET /api/v1/health</t>
+  </si>
+  <si>
+    <t>HTTP 200 response</t>
+  </si>
+  <si>
+    <t>Auth login — valid credentials return access token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST /auth/login with admin credentials
+2. Verify response has accessToken
+3. Verify user.email matches input</t>
+  </si>
+  <si>
+    <t>HTTP 200 + valid JWT token returned</t>
+  </si>
+  <si>
+    <t>Auth login — invalid credentials return 401</t>
+  </si>
+  <si>
+    <t>1. POST /auth/login with invalid email/password</t>
+  </si>
+  <si>
+    <t>HTTP 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>02-tg2-tg3-tg4-navigation.spec.ts</t>
+  </si>
+  <si>
+    <t>Admin login — Create new button and Admin dropdown visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as admin
+2. Dismiss onboarding wizard
+3. Verify "Create new" button visible
+4. Verify Admin button in sidebar</t>
+  </si>
+  <si>
+    <t>Both Create new and Admin dropdown are visible</t>
+  </si>
+  <si>
+    <t>Workspace pages load — Audit Groups, Pulse, Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate /audit-groups → verify no error
+2. Navigate /pulse → verify "active audit" text
+3. Navigate /policies → verify "create policy" button</t>
+  </si>
+  <si>
+    <t>All 3 workspace pages load without errors</t>
+  </si>
+  <si>
+    <t>Contributor login — Admin, Policies, Pulse, Integrations NOT visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as contributor
+2. Verify Admin button NOT visible
+3. Verify /policies link NOT visible
+4. Verify /pulse link NOT visible
+5. Verify /integrations link NOT visible</t>
+  </si>
+  <si>
+    <t>All 4 restricted tabs hidden for contributor</t>
+  </si>
+  <si>
+    <t>All Admin sub-tabs load without errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as admin
+2. /admin → verify Add user button
+3. /admin/roles → verify Create role button
+4. /admin/integrations → no error
+5. /admin/features → no error
+6. /admin/activity → no error
+7. /admin/organization → no error</t>
+  </si>
+  <si>
+    <t>All 6 admin sub-pages load without errors</t>
+  </si>
+  <si>
+    <t>03-tg6-audit-lifecycle.spec.ts</t>
+  </si>
+  <si>
+    <t>Step 1-2: Audit tiles are visible on home page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login as admin
+2. Navigate to /
+3. Verify at least one audit tile link exists</t>
+  </si>
+  <si>
+    <t>At least 1 audit tile visible</t>
+  </si>
+  <si>
+    <t>Step 3: Search box is visible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to /
+2. Verify search input with placeholder "Search" is visible</t>
+  </si>
+  <si>
+    <t>Search box is displayed</t>
+  </si>
+  <si>
+    <t>Step 4: Search by framework name filters matching audits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Type "SOC" in search box
+2. Wait 2 seconds
+3. Verify audit tiles filter (count &gt;= 0)</t>
+  </si>
+  <si>
+    <t>Search filters audits by framework name</t>
+  </si>
+  <si>
+    <t>Step 5: Search by audit name filters matching audits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Get first audit tile text
+2. Type first 5 chars in search
+3. Verify page still renders main content</t>
+  </si>
+  <si>
+    <t>Search filters by partial audit name</t>
+  </si>
+  <si>
+    <t>Step 6: Click audit tile — shows 5 tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click first audit tile
+2. Wait for /audit/ URL
+3. Verify &gt;= 5 tabs visible
+4. Verify: Dashboard, Workspace, Internal Audit, Document, Action Plan</t>
+  </si>
+  <si>
+    <t>Audit detail page shows all 5 tabs</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>04-mc-availability.spec.ts</t>
+  </si>
+  <si>
+    <t>Mission Control — app is reachable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET {mcUrl}/login
+2. Verify HTTP status &lt; 500</t>
+  </si>
+  <si>
+    <t>MC responds without server error</t>
+  </si>
+  <si>
+    <t>Mission Control — page renders login form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open {mcUrl}/login in browser
+2. Verify email input field is visible</t>
+  </si>
+  <si>
+    <t>MC login form renders</t>
+  </si>
+  <si>
+    <t>Audit Portal</t>
+  </si>
+  <si>
+    <t>05-audit-availability.spec.ts</t>
+  </si>
+  <si>
+    <t>Audit Portal — app is reachable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET {auditUrl}/login
+2. Verify HTTP status &lt; 500
+(Skipped on Prod — not ready)</t>
+  </si>
+  <si>
+    <t>Audit Portal responds without error</t>
+  </si>
+  <si>
+    <t>POC only</t>
+  </si>
+  <si>
+    <t>Audit Portal — page renders login form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open {auditUrl}/login in browser
+2. Verify email input visible
+(Skipped on Prod — not ready)</t>
+  </si>
+  <si>
+    <t>Audit Portal login form renders</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>06-api-endpoints.spec.ts</t>
+  </si>
+  <si>
+    <t>Auth — obtain token for API tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. POST /auth/login with admin creds
+2. Store accessToken</t>
+  </si>
+  <si>
+    <t>Token obtained successfully</t>
+  </si>
+  <si>
+    <t>GET /users/me — returns current user profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET /users/me with Bearer token
+2. Verify has id, email, roles</t>
+  </si>
+  <si>
+    <t>HTTP 200 + user profile</t>
+  </si>
+  <si>
+    <t>GET /frameworks — returns list with required fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET /frameworks
+2. Verify array length &gt; 0
+3. Verify each has id, name, sourceType</t>
+  </si>
+  <si>
+    <t>HTTP 200 + non-empty framework list</t>
+  </si>
+  <si>
+    <t>GET /audits — returns audit list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET /audits
+2. Verify HTTP 200 + returns array</t>
+  </si>
+  <si>
+    <t>HTTP 200 + audit array</t>
+  </si>
+  <si>
+    <t>GET /users — returns user list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET /users
+2. Verify length &gt; 0
+3. Verify has id, email</t>
+  </si>
+  <si>
+    <t>HTTP 200 + user list</t>
+  </si>
+  <si>
+    <t>GET /policies — returns policy list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET /policies
+2. Verify HTTP 200</t>
+  </si>
+  <si>
+    <t>HTTP 200</t>
+  </si>
+  <si>
+    <t>GET /business-units — returns list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. GET /business-units
+2. Verify status &lt; 500 (403 = alive but restricted)</t>
+  </si>
+  <si>
+    <t>No server error (200 or 403)</t>
+  </si>
+  <si>
+    <t>API response time — no endpoint exceeds 5s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Hit /health, /frameworks, /audits, /users, /policies
+2. Measure response time
+3. Verify none &gt; 5000ms</t>
+  </si>
+  <si>
+    <t>All endpoints respond within 5 seconds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1944,15 +2285,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2285,16 +2633,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J65"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="134" customWidth="1"/>
-    <col min="5" max="5" width="42.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.25" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2329,7 +2677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2337,7 +2685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2427,7 +2775,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2467,7 +2815,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -2624,7 +2972,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -2667,7 +3015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -2693,7 +3041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -2719,7 +3067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -2745,7 +3093,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -2771,7 +3119,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -2837,7 +3185,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>64</v>
       </c>
@@ -2892,7 +3240,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -2918,7 +3266,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -2944,7 +3292,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -3068,7 +3416,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -3094,7 +3442,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>77</v>
       </c>
@@ -3120,7 +3468,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>77</v>
       </c>
@@ -3175,7 +3523,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -3201,7 +3549,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>77</v>
       </c>
@@ -3256,7 +3604,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -3282,7 +3630,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -3308,7 +3656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>77</v>
       </c>
@@ -3334,7 +3682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -3360,7 +3708,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>77</v>
       </c>
@@ -3444,7 +3792,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>116</v>
       </c>
@@ -3458,7 +3806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -3600,7 +3948,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>118</v>
       </c>
@@ -3626,7 +3974,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>130</v>
       </c>
@@ -3652,7 +4000,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>130</v>
       </c>
@@ -3678,7 +4026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>130</v>
       </c>
@@ -3704,7 +4052,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>130</v>
       </c>
@@ -3730,7 +4078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>130</v>
       </c>
@@ -3843,7 +4191,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>145</v>
       </c>
@@ -3869,7 +4217,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>147</v>
       </c>
@@ -3895,7 +4243,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>149</v>
       </c>
@@ -3986,16 +4334,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:J44 A65:J65 A45:E64 G45:J56 H64:J64 H57:J57 H58:J58 H59:J59 H60:J60 H61:J61 H62:J62 H63:J63" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -4072,23 +4417,20 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="B4" r:id="rId2"/>
+    <hyperlink ref="B5" r:id="rId3"/>
+    <hyperlink ref="B6" r:id="rId4"/>
+    <hyperlink ref="B7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:C7" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4924,16 +5266,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H32" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5077,16 +5416,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:K4" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J489"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -20738,8 +21074,702 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:J489" numberStoredAsText="1"/>
-  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="100" style="2" customWidth="1"/>
+    <col min="6" max="6" width="50" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="G2" t="s">
+        <v>640</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D3" t="s">
+        <v>641</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="G3" t="s">
+        <v>640</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>636</v>
+      </c>
+      <c r="D4" t="s">
+        <v>644</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="G4" t="s">
+        <v>640</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>636</v>
+      </c>
+      <c r="D5" t="s">
+        <v>647</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="G5" t="s">
+        <v>640</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>650</v>
+      </c>
+      <c r="D6" t="s">
+        <v>651</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="G6" t="s">
+        <v>640</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>650</v>
+      </c>
+      <c r="D7" t="s">
+        <v>654</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="G7" t="s">
+        <v>640</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>650</v>
+      </c>
+      <c r="D8" t="s">
+        <v>657</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="G8" t="s">
+        <v>640</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>650</v>
+      </c>
+      <c r="D9" t="s">
+        <v>660</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G9" t="s">
+        <v>640</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>663</v>
+      </c>
+      <c r="D10" t="s">
+        <v>664</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="G10" t="s">
+        <v>640</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" t="s">
+        <v>663</v>
+      </c>
+      <c r="D11" t="s">
+        <v>667</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="G11" t="s">
+        <v>640</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>663</v>
+      </c>
+      <c r="D12" t="s">
+        <v>670</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="G12" t="s">
+        <v>640</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>663</v>
+      </c>
+      <c r="D13" t="s">
+        <v>673</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="G13" t="s">
+        <v>640</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>663</v>
+      </c>
+      <c r="D14" t="s">
+        <v>676</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="G14" t="s">
+        <v>640</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>679</v>
+      </c>
+      <c r="C15" t="s">
+        <v>680</v>
+      </c>
+      <c r="D15" t="s">
+        <v>681</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="G15" t="s">
+        <v>640</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>679</v>
+      </c>
+      <c r="C16" t="s">
+        <v>680</v>
+      </c>
+      <c r="D16" t="s">
+        <v>684</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="G16" t="s">
+        <v>640</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>687</v>
+      </c>
+      <c r="C17" t="s">
+        <v>688</v>
+      </c>
+      <c r="D17" t="s">
+        <v>689</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G17" t="s">
+        <v>692</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>687</v>
+      </c>
+      <c r="C18" t="s">
+        <v>688</v>
+      </c>
+      <c r="D18" t="s">
+        <v>693</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="G18" t="s">
+        <v>692</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>696</v>
+      </c>
+      <c r="C19" t="s">
+        <v>697</v>
+      </c>
+      <c r="D19" t="s">
+        <v>698</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="G19" t="s">
+        <v>640</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>696</v>
+      </c>
+      <c r="C20" t="s">
+        <v>697</v>
+      </c>
+      <c r="D20" t="s">
+        <v>701</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="G20" t="s">
+        <v>640</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>696</v>
+      </c>
+      <c r="C21" t="s">
+        <v>697</v>
+      </c>
+      <c r="D21" t="s">
+        <v>704</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="G21" t="s">
+        <v>640</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>696</v>
+      </c>
+      <c r="C22" t="s">
+        <v>697</v>
+      </c>
+      <c r="D22" t="s">
+        <v>707</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="G22" t="s">
+        <v>640</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>696</v>
+      </c>
+      <c r="C23" t="s">
+        <v>697</v>
+      </c>
+      <c r="D23" t="s">
+        <v>710</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="G23" t="s">
+        <v>640</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>696</v>
+      </c>
+      <c r="C24" t="s">
+        <v>697</v>
+      </c>
+      <c r="D24" t="s">
+        <v>713</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="G24" t="s">
+        <v>640</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>696</v>
+      </c>
+      <c r="C25" t="s">
+        <v>697</v>
+      </c>
+      <c r="D25" t="s">
+        <v>716</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="G25" t="s">
+        <v>640</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>696</v>
+      </c>
+      <c r="C26" t="s">
+        <v>697</v>
+      </c>
+      <c r="D26" t="s">
+        <v>719</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="G26" t="s">
+        <v>640</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AA6BA3-5AB2-4BAF-98F9-F82FBD6AF2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C4A165-88C2-43CF-A36D-9B5F90397103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="727" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="727" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5562" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5559" uniqueCount="696">
   <si>
     <t>Test case</t>
   </si>
@@ -2502,7 +2502,7 @@
   <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="49.58203125" customWidth="1"/>
+    <col min="2" max="2" width="86.9140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -22008,7 +22008,7 @@
         <v>685</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>686</v>
@@ -22080,7 +22080,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A3:C5 A2 C2 A7:C10 A6 C6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A3:C3 A2 C2 A7:C10 A6 C6 A5:C5 A4 C4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C4A165-88C2-43CF-A36D-9B5F90397103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D73947-77AE-48DD-B85E-1DEA1B513712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="727" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5559" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5559" uniqueCount="695">
   <si>
     <t>Test case</t>
   </si>
@@ -2109,9 +2109,6 @@
   </si>
   <si>
     <t>• Push to GitHub for CI runs to pick up changes.</t>
-  </si>
-  <si>
-    <t>keerthi@quantarra.io, deepak@quantarra.io</t>
   </si>
 </sst>
 </file>
@@ -4294,7 +4291,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I56 A71:I71 A65:C65 H65:I65 A66:C66 H66:I66 A67:C67 H67:I67 A68:C68 H68:I68 A69:C69 H69:I69 A70:C70 H70:I70 A64:F64 A57:F57 H57:I57 A58:F58 H58:I58 A59:F59 H59:I59 A60:F60 H60:I60 A61:F61 H61:I61 A62:F62 H62:I62 A63:F63 H63:I63 H64:I64" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I56 A71:I71 A65:C65 H65:I65 A66:C66 H66:I66 A67:C67 H67:I67 A68:C68 H68:I68 A69:C69 H69:I69 A70:C70 H70:I70 A64:F64 A57 H57:I57 A58:F58 H58:I58 A59:F59 H59:I59 A60:F60 H60:I60 A61:F61 H61:I61 A62:F62 H62:I62 A63:F63 H63:I63 H64:I64 C57:F57" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -22029,8 +22026,8 @@
       <c r="A6" t="s">
         <v>690</v>
       </c>
-      <c r="B6" t="s">
-        <v>695</v>
+      <c r="B6" s="1" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -22078,6 +22075,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{6794E79B-E8D6-4D28-8342-139A5ED5576A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A1:C1 A3:C3 A2 C2 A7:C10 A6 C6 A5:C5 A4 C4" numberStoredAsText="1"/>

--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D73947-77AE-48DD-B85E-1DEA1B513712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97F4D5F-635D-441E-BEDB-A4110E9B66FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="727" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-1400" windowWidth="19420" windowHeight="11500" tabRatio="778" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5559" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5663" uniqueCount="712">
   <si>
     <t>Test case</t>
   </si>
@@ -2109,13 +2109,64 @@
   </si>
   <si>
     <t>• Push to GitHub for CI runs to pick up changes.</t>
+  </si>
+  <si>
+    <t>Audit work space - Filters</t>
+  </si>
+  <si>
+    <t>TG-7</t>
+  </si>
+  <si>
+    <t>Login with Administrator user - Search SOC 2 Type 2 Audit - Select the first audit - Navigate to Audit workspace -&gt; Controls -&gt; All Controls</t>
+  </si>
+  <si>
+    <t>//*[@id="tabpanel-ws"]/div/div[1]/div/button</t>
+  </si>
+  <si>
+    <t>Click on the Filter Button on the Top right Corner</t>
+  </si>
+  <si>
+    <t>Verify Filter Slide bar appreas</t>
+  </si>
+  <si>
+    <t>Verify the Filter Slide bar dissapears</t>
+  </si>
+  <si>
+    <t>Scroll Down to identify Submission status - Select Status " In Progress" and Click on Apply Filter</t>
+  </si>
+  <si>
+    <t>Audit workspace -&gt; Controls -&gt; All Controls shows Controils only with In progress status.</t>
+  </si>
+  <si>
+    <t>Filter Button to Show count badge the "1" that reflects the Number of Filters applied</t>
+  </si>
+  <si>
+    <t>With the filter applied, Click on the first control to open the control and view.</t>
+  </si>
+  <si>
+    <t>Navigate back to All controls page - The filter should still be applied</t>
+  </si>
+  <si>
+    <t>Click on the Filter Button on the Top right Corner again</t>
+  </si>
+  <si>
+    <t>Scroll Down to click on "Clear all" Button, and click Apply filter button</t>
+  </si>
+  <si>
+    <t>The Filter slide bar is closed and navigation is back to All controls tab again</t>
+  </si>
+  <si>
+    <t>All Controls tab should show Controls with all the status, Scroll down to perform a random check</t>
+  </si>
+  <si>
+    <t>keerthi@quantarra.io, deepak@quantarra.io</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2127,6 +2178,12 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2496,13 +2553,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I71"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I85"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="86.9140625" customWidth="1"/>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="95.25" customWidth="1"/>
+    <col min="4" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2531,7 +2593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2539,7 +2601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2565,7 +2627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2594,7 +2656,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2623,7 +2685,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2634,7 +2696,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2663,7 +2725,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2692,7 +2754,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2721,7 +2783,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -2750,7 +2812,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -2779,7 +2841,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -2808,7 +2870,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -2819,7 +2881,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2848,7 +2910,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -2874,7 +2936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2900,7 +2962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2926,7 +2988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2952,7 +3014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -2960,7 +3022,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2989,7 +3051,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -3018,7 +3080,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3044,7 +3106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -3073,7 +3135,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -3099,7 +3161,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -3125,7 +3187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -3133,7 +3195,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3162,7 +3224,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -3191,7 +3253,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -3220,7 +3282,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -3249,7 +3311,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -3275,7 +3337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -3301,7 +3363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -3327,7 +3389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -3356,7 +3418,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -3382,7 +3444,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -3408,7 +3470,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -3437,7 +3499,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>87</v>
       </c>
@@ -3463,7 +3525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -3489,7 +3551,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -3515,7 +3577,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>93</v>
       </c>
@@ -3541,7 +3603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>95</v>
       </c>
@@ -3567,7 +3629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>97</v>
       </c>
@@ -3596,7 +3658,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>100</v>
       </c>
@@ -3625,7 +3687,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>103</v>
       </c>
@@ -3633,7 +3695,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -3659,7 +3721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -3688,7 +3750,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -3717,7 +3779,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -3746,7 +3808,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>36</v>
       </c>
@@ -3775,7 +3837,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -3801,7 +3863,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>76</v>
       </c>
@@ -3827,7 +3889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>77</v>
       </c>
@@ -3853,7 +3915,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>80</v>
       </c>
@@ -3879,7 +3941,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -3905,7 +3967,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -3931,7 +3993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>87</v>
       </c>
@@ -3960,7 +4022,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -3989,7 +4051,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>91</v>
       </c>
@@ -4018,7 +4080,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>93</v>
       </c>
@@ -4044,7 +4106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -4070,7 +4132,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>97</v>
       </c>
@@ -4096,7 +4158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>100</v>
       </c>
@@ -4125,7 +4187,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>131</v>
       </c>
@@ -4154,7 +4216,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>134</v>
       </c>
@@ -4177,13 +4239,16 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>136</v>
       </c>
       <c r="B66" t="s">
         <v>137</v>
       </c>
+      <c r="C66" t="s">
+        <v>106</v>
+      </c>
       <c r="D66" t="s">
         <v>14</v>
       </c>
@@ -4197,13 +4262,16 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>138</v>
       </c>
       <c r="B67" t="s">
         <v>139</v>
       </c>
+      <c r="C67" t="s">
+        <v>106</v>
+      </c>
       <c r="D67" t="s">
         <v>14</v>
       </c>
@@ -4217,13 +4285,16 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>140</v>
       </c>
       <c r="B68" t="s">
         <v>141</v>
       </c>
+      <c r="C68" t="s">
+        <v>106</v>
+      </c>
       <c r="D68" t="s">
         <v>14</v>
       </c>
@@ -4237,13 +4308,16 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>142</v>
       </c>
       <c r="B69" t="s">
         <v>143</v>
       </c>
+      <c r="C69" t="s">
+        <v>106</v>
+      </c>
       <c r="D69" t="s">
         <v>14</v>
       </c>
@@ -4260,13 +4334,16 @@
         <v>144</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>145</v>
       </c>
       <c r="B70" t="s">
         <v>146</v>
       </c>
+      <c r="C70" t="s">
+        <v>106</v>
+      </c>
       <c r="D70" t="s">
         <v>14</v>
       </c>
@@ -4280,18 +4357,344 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>695</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" t="s">
+        <v>696</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" t="s">
+        <v>697</v>
+      </c>
+      <c r="C73" t="s">
+        <v>696</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" t="s">
+        <v>699</v>
+      </c>
+      <c r="C74" t="s">
+        <v>696</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" t="s">
+        <v>700</v>
+      </c>
+      <c r="C75" t="s">
+        <v>696</v>
+      </c>
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>36</v>
+      </c>
+      <c r="B76" t="s">
+        <v>702</v>
+      </c>
+      <c r="C76" t="s">
+        <v>696</v>
+      </c>
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" t="s">
+        <v>701</v>
+      </c>
+      <c r="C77" t="s">
+        <v>696</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>703</v>
+      </c>
+      <c r="C78" t="s">
+        <v>696</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>704</v>
+      </c>
+      <c r="C79" t="s">
+        <v>696</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" t="s">
+        <v>705</v>
+      </c>
+      <c r="C80" t="s">
+        <v>696</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>82</v>
+      </c>
+      <c r="B81" t="s">
+        <v>706</v>
+      </c>
+      <c r="C81" t="s">
+        <v>696</v>
+      </c>
+      <c r="D81" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" t="s">
+        <v>707</v>
+      </c>
+      <c r="C82" t="s">
+        <v>696</v>
+      </c>
+      <c r="D82" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83" t="s">
+        <v>708</v>
+      </c>
+      <c r="C83" t="s">
+        <v>696</v>
+      </c>
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" t="s">
+        <v>14</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" t="s">
+        <v>709</v>
+      </c>
+      <c r="C84" t="s">
+        <v>696</v>
+      </c>
+      <c r="D84" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" t="s">
+        <v>710</v>
+      </c>
+      <c r="C85" t="s">
+        <v>696</v>
+      </c>
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I56 A71:I71 A65:C65 H65:I65 A66:C66 H66:I66 A67:C67 H67:I67 A68:C68 H68:I68 A69:C69 H69:I69 A70:C70 H70:I70 A64:F64 A57 H57:I57 A58:F58 H58:I58 A59:F59 H59:I59 A60:F60 H60:I60 A61:F61 H61:I61 A62:F62 H62:I62 A63:F63 H63:I63 H64:I64 C57:F57" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I56 A71 A65:C65 H65:I65 A66:B66 H66:I66 A67:B67 H67:I67 A68:B68 H68:I68 A69:B69 H69:I69 A70:B70 H70:I70 A64:F64 A57 H57:I57 A58:F58 H58:I58 A59:F59 H59:I59 A60:F60 H60:I60 A61:F61 H61:I61 A62:F62 H62:I62 A63:F63 H63:I63 H64:I64 C57:F57 C71:I71" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4299,12 +4702,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.25" customWidth="1"/>
+    <col min="2" max="2" width="99.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4327,7 +4730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>149</v>
       </c>
@@ -4335,7 +4738,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -4355,7 +4758,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4375,7 +4778,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -4395,7 +4798,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4415,7 +4818,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -4438,7 +4841,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -4461,7 +4864,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -4484,7 +4887,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>77</v>
       </c>
@@ -4504,7 +4907,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>80</v>
       </c>
@@ -4527,7 +4930,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -4550,7 +4953,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -4570,7 +4973,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -4593,7 +4996,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -4616,7 +5019,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>91</v>
       </c>
@@ -4639,7 +5042,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>93</v>
       </c>
@@ -4662,7 +5065,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -4685,7 +5088,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -4705,7 +5108,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -4725,7 +5128,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -4733,7 +5136,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -4756,7 +5159,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -4776,7 +5179,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -4796,7 +5199,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -4819,7 +5222,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -4842,7 +5245,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -4865,7 +5268,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>76</v>
       </c>
@@ -4888,7 +5291,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>77</v>
       </c>
@@ -4911,7 +5314,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -4934,7 +5337,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -4957,7 +5360,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>84</v>
       </c>
@@ -4980,7 +5383,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>87</v>
       </c>
@@ -5003,7 +5406,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>89</v>
       </c>
@@ -5026,7 +5429,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>91</v>
       </c>
@@ -5049,22 +5452,22 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>100</v>
       </c>
@@ -5072,7 +5475,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G39" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G6 A35:G39 A34 C34:G34 A27:G33 A25 C25:G25 A26 C26:G26 A11:G24 A8 C8:G8 A7 C7:G7 A9 C9:G9 A10 C10:G10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5080,9 +5483,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>196</v>
       </c>
@@ -5108,7 +5511,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>204</v>
       </c>
@@ -5134,7 +5537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>211</v>
       </c>
@@ -5160,7 +5563,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>211</v>
       </c>
@@ -5186,7 +5589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>211</v>
       </c>
@@ -5212,7 +5615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>211</v>
       </c>
@@ -5238,7 +5641,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>211</v>
       </c>
@@ -5264,7 +5667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>211</v>
       </c>
@@ -5290,7 +5693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>211</v>
       </c>
@@ -5316,7 +5719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>211</v>
       </c>
@@ -5342,7 +5745,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>211</v>
       </c>
@@ -5368,7 +5771,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>211</v>
       </c>
@@ -5394,7 +5797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>211</v>
       </c>
@@ -5420,7 +5823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>211</v>
       </c>
@@ -5446,7 +5849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>224</v>
       </c>
@@ -5472,7 +5875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>228</v>
       </c>
@@ -5498,7 +5901,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>229</v>
       </c>
@@ -5524,7 +5927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>230</v>
       </c>
@@ -5550,7 +5953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>231</v>
       </c>
@@ -5576,7 +5979,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>232</v>
       </c>
@@ -5602,7 +6005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>233</v>
       </c>
@@ -5628,7 +6031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>234</v>
       </c>
@@ -5654,7 +6057,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>235</v>
       </c>
@@ -5680,7 +6083,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>236</v>
       </c>
@@ -5706,7 +6109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>237</v>
       </c>
@@ -5732,7 +6135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>238</v>
       </c>
@@ -5758,7 +6161,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>239</v>
       </c>
@@ -5784,7 +6187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>240</v>
       </c>
@@ -5810,7 +6213,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>241</v>
       </c>
@@ -5836,7 +6239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>242</v>
       </c>
@@ -5862,7 +6265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>243</v>
       </c>
@@ -5888,7 +6291,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>244</v>
       </c>
@@ -5925,9 +6328,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J489"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>246</v>
       </c>
@@ -5959,7 +6362,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5991,7 +6394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6023,7 +6426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6055,7 +6458,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6087,7 +6490,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6119,7 +6522,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6151,7 +6554,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6183,7 +6586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6215,7 +6618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6247,7 +6650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6279,7 +6682,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6311,7 +6714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6343,7 +6746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6375,7 +6778,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6407,7 +6810,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6439,7 +6842,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6471,7 +6874,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6503,7 +6906,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6535,7 +6938,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6567,7 +6970,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6599,7 +7002,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6631,7 +7034,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6663,7 +7066,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6695,7 +7098,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6727,7 +7130,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6759,7 +7162,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6791,7 +7194,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6823,7 +7226,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6855,7 +7258,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6887,7 +7290,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6919,7 +7322,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6951,7 +7354,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6983,7 +7386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -7015,7 +7418,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -7047,7 +7450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -7079,7 +7482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7111,7 +7514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7143,7 +7546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7175,7 +7578,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7207,7 +7610,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7239,7 +7642,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7271,7 +7674,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7303,7 +7706,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7335,7 +7738,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7367,7 +7770,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7399,7 +7802,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7431,7 +7834,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7463,7 +7866,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7495,7 +7898,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7527,7 +7930,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7559,7 +7962,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7591,7 +7994,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7623,7 +8026,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -7655,7 +8058,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -7687,7 +8090,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -7719,7 +8122,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -7751,7 +8154,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -7783,7 +8186,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -7815,7 +8218,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -7847,7 +8250,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -7879,7 +8282,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7911,7 +8314,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7943,7 +8346,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7975,7 +8378,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -8007,7 +8410,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -8039,7 +8442,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -8071,7 +8474,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -8103,7 +8506,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -8135,7 +8538,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -8167,7 +8570,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -8199,7 +8602,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -8231,7 +8634,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -8263,7 +8666,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -8295,7 +8698,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -8327,7 +8730,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -8359,7 +8762,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -8391,7 +8794,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -8423,7 +8826,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -8455,7 +8858,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -8487,7 +8890,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -8519,7 +8922,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -8551,7 +8954,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -8583,7 +8986,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -8615,7 +9018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -8647,7 +9050,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -8679,7 +9082,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -8711,7 +9114,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -8743,7 +9146,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -8775,7 +9178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -8807,7 +9210,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -8839,7 +9242,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -8871,7 +9274,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -8903,7 +9306,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -8935,7 +9338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -8967,7 +9370,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -8999,7 +9402,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9031,7 +9434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9063,7 +9466,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9095,7 +9498,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -9127,7 +9530,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -9159,7 +9562,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -9191,7 +9594,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -9223,7 +9626,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -9255,7 +9658,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -9287,7 +9690,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -9319,7 +9722,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -9351,7 +9754,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -9383,7 +9786,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -9415,7 +9818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -9447,7 +9850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -9479,7 +9882,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -9511,7 +9914,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -9543,7 +9946,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -9575,7 +9978,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -9607,7 +10010,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -9639,7 +10042,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -9671,7 +10074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -9703,7 +10106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -9735,7 +10138,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -9767,7 +10170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -9799,7 +10202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -9831,7 +10234,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -9863,7 +10266,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -9895,7 +10298,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -9927,7 +10330,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -9959,7 +10362,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -9991,7 +10394,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -10023,7 +10426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10055,7 +10458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10087,7 +10490,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10119,7 +10522,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10151,7 +10554,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -10183,7 +10586,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -10215,7 +10618,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -10247,7 +10650,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -10279,7 +10682,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -10311,7 +10714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -10343,7 +10746,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -10375,7 +10778,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -10407,7 +10810,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -10439,7 +10842,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -10471,7 +10874,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -10503,7 +10906,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -10535,7 +10938,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -10567,7 +10970,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -10599,7 +11002,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -10631,7 +11034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -10663,7 +11066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -10695,7 +11098,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -10727,7 +11130,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -10759,7 +11162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -10791,7 +11194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -10823,7 +11226,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -10855,7 +11258,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -10887,7 +11290,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -10919,7 +11322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -10951,7 +11354,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -10983,7 +11386,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -11015,7 +11418,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -11047,7 +11450,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -11079,7 +11482,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -11111,7 +11514,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -11143,7 +11546,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -11175,7 +11578,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -11207,7 +11610,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -11239,7 +11642,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -11271,7 +11674,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -11303,7 +11706,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -11335,7 +11738,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -11367,7 +11770,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -11399,7 +11802,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -11431,7 +11834,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -11463,7 +11866,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -11495,7 +11898,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -11527,7 +11930,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -11559,7 +11962,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -11591,7 +11994,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -11623,7 +12026,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -11655,7 +12058,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -11687,7 +12090,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -11719,7 +12122,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -11751,7 +12154,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -11783,7 +12186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -11815,7 +12218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -11847,7 +12250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -11879,7 +12282,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -11911,7 +12314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -11943,7 +12346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -11975,7 +12378,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -12007,7 +12410,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -12039,7 +12442,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -12071,7 +12474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -12103,7 +12506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -12135,7 +12538,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -12167,7 +12570,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -12199,7 +12602,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -12231,7 +12634,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -12263,7 +12666,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -12295,7 +12698,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -12327,7 +12730,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -12359,7 +12762,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -12391,7 +12794,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -12423,7 +12826,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -12455,7 +12858,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -12487,7 +12890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -12519,7 +12922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -12551,7 +12954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -12583,7 +12986,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -12615,7 +13018,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -12647,7 +13050,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -12679,7 +13082,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -12711,7 +13114,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -12743,7 +13146,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -12775,7 +13178,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -12807,7 +13210,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -12839,7 +13242,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -12871,7 +13274,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -12903,7 +13306,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -12935,7 +13338,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -12967,7 +13370,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -12999,7 +13402,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -13031,7 +13434,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -13063,7 +13466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -13095,7 +13498,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -13127,7 +13530,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -13159,7 +13562,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -13191,7 +13594,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -13223,7 +13626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -13255,7 +13658,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -13287,7 +13690,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -13319,7 +13722,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -13351,7 +13754,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -13383,7 +13786,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -13415,7 +13818,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -13447,7 +13850,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -13479,7 +13882,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -13511,7 +13914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -13543,7 +13946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -13575,7 +13978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -13607,7 +14010,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -13639,7 +14042,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -13671,7 +14074,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -13703,7 +14106,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -13735,7 +14138,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -13767,7 +14170,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -13799,7 +14202,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -13831,7 +14234,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -13863,7 +14266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -13895,7 +14298,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -13927,7 +14330,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -13959,7 +14362,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -13991,7 +14394,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -14023,7 +14426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -14055,7 +14458,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -14087,7 +14490,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -14119,7 +14522,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -14151,7 +14554,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -14183,7 +14586,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -14215,7 +14618,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -14247,7 +14650,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -14279,7 +14682,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -14311,7 +14714,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -14343,7 +14746,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -14375,7 +14778,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -14407,7 +14810,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -14439,7 +14842,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -14471,7 +14874,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -14503,7 +14906,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -14535,7 +14938,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -14567,7 +14970,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -14599,7 +15002,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -14631,7 +15034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -14663,7 +15066,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -14695,7 +15098,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -14727,7 +15130,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -14759,7 +15162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -14791,7 +15194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -14823,7 +15226,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -14855,7 +15258,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -14887,7 +15290,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -14919,7 +15322,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -14951,7 +15354,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -14983,7 +15386,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -15015,7 +15418,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -15047,7 +15450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -15079,7 +15482,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -15111,7 +15514,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -15143,7 +15546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -15175,7 +15578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -15207,7 +15610,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -15239,7 +15642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -15271,7 +15674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -15303,7 +15706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -15335,7 +15738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -15367,7 +15770,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -15399,7 +15802,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -15431,7 +15834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
@@ -15463,7 +15866,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -15495,7 +15898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -15527,7 +15930,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>300</v>
       </c>
@@ -15559,7 +15962,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>301</v>
       </c>
@@ -15591,7 +15994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>302</v>
       </c>
@@ -15623,7 +16026,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>303</v>
       </c>
@@ -15655,7 +16058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>304</v>
       </c>
@@ -15687,7 +16090,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>305</v>
       </c>
@@ -15719,7 +16122,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>306</v>
       </c>
@@ -15751,7 +16154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>307</v>
       </c>
@@ -15783,7 +16186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>308</v>
       </c>
@@ -15815,7 +16218,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>309</v>
       </c>
@@ -15847,7 +16250,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>310</v>
       </c>
@@ -15879,7 +16282,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>311</v>
       </c>
@@ -15911,7 +16314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>312</v>
       </c>
@@ -15943,7 +16346,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>313</v>
       </c>
@@ -15975,7 +16378,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>314</v>
       </c>
@@ -16007,7 +16410,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>315</v>
       </c>
@@ -16039,7 +16442,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>316</v>
       </c>
@@ -16071,7 +16474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>317</v>
       </c>
@@ -16103,7 +16506,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>318</v>
       </c>
@@ -16135,7 +16538,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>319</v>
       </c>
@@ -16167,7 +16570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>320</v>
       </c>
@@ -16199,7 +16602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>321</v>
       </c>
@@ -16231,7 +16634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>322</v>
       </c>
@@ -16263,7 +16666,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>323</v>
       </c>
@@ -16295,7 +16698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>324</v>
       </c>
@@ -16327,7 +16730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>325</v>
       </c>
@@ -16359,7 +16762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>326</v>
       </c>
@@ -16391,7 +16794,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>327</v>
       </c>
@@ -16423,7 +16826,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>328</v>
       </c>
@@ -16455,7 +16858,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>329</v>
       </c>
@@ -16487,7 +16890,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>330</v>
       </c>
@@ -16519,7 +16922,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>331</v>
       </c>
@@ -16551,7 +16954,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>332</v>
       </c>
@@ -16583,7 +16986,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>333</v>
       </c>
@@ -16615,7 +17018,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>334</v>
       </c>
@@ -16647,7 +17050,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>335</v>
       </c>
@@ -16679,7 +17082,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>336</v>
       </c>
@@ -16711,7 +17114,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>337</v>
       </c>
@@ -16743,7 +17146,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>338</v>
       </c>
@@ -16775,7 +17178,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>339</v>
       </c>
@@ -16807,7 +17210,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>340</v>
       </c>
@@ -16839,7 +17242,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>341</v>
       </c>
@@ -16871,7 +17274,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>342</v>
       </c>
@@ -16903,7 +17306,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>343</v>
       </c>
@@ -16935,7 +17338,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>344</v>
       </c>
@@ -16967,7 +17370,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>345</v>
       </c>
@@ -16999,7 +17402,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>346</v>
       </c>
@@ -17031,7 +17434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>347</v>
       </c>
@@ -17063,7 +17466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>348</v>
       </c>
@@ -17095,7 +17498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>349</v>
       </c>
@@ -17127,7 +17530,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>350</v>
       </c>
@@ -17159,7 +17562,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>351</v>
       </c>
@@ -17191,7 +17594,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>352</v>
       </c>
@@ -17223,7 +17626,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>353</v>
       </c>
@@ -17255,7 +17658,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>354</v>
       </c>
@@ -17287,7 +17690,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>355</v>
       </c>
@@ -17319,7 +17722,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>356</v>
       </c>
@@ -17351,7 +17754,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>357</v>
       </c>
@@ -17383,7 +17786,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>358</v>
       </c>
@@ -17415,7 +17818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>359</v>
       </c>
@@ -17447,7 +17850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>360</v>
       </c>
@@ -17479,7 +17882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>361</v>
       </c>
@@ -17511,7 +17914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>362</v>
       </c>
@@ -17543,7 +17946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>363</v>
       </c>
@@ -17575,7 +17978,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>364</v>
       </c>
@@ -17607,7 +18010,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>365</v>
       </c>
@@ -17639,7 +18042,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>366</v>
       </c>
@@ -17671,7 +18074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>367</v>
       </c>
@@ -17703,7 +18106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>368</v>
       </c>
@@ -17735,7 +18138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>369</v>
       </c>
@@ -17767,7 +18170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>370</v>
       </c>
@@ -17799,7 +18202,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>371</v>
       </c>
@@ -17831,7 +18234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>372</v>
       </c>
@@ -17863,7 +18266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>373</v>
       </c>
@@ -17895,7 +18298,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>374</v>
       </c>
@@ -17927,7 +18330,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>375</v>
       </c>
@@ -17959,7 +18362,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>376</v>
       </c>
@@ -17991,7 +18394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>377</v>
       </c>
@@ -18023,7 +18426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>378</v>
       </c>
@@ -18055,7 +18458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>379</v>
       </c>
@@ -18087,7 +18490,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>380</v>
       </c>
@@ -18119,7 +18522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>381</v>
       </c>
@@ -18151,7 +18554,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>382</v>
       </c>
@@ -18183,7 +18586,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>383</v>
       </c>
@@ -18215,7 +18618,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>384</v>
       </c>
@@ -18247,7 +18650,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>385</v>
       </c>
@@ -18279,7 +18682,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>386</v>
       </c>
@@ -18311,7 +18714,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>387</v>
       </c>
@@ -18343,7 +18746,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>388</v>
       </c>
@@ -18375,7 +18778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>389</v>
       </c>
@@ -18407,7 +18810,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>390</v>
       </c>
@@ -18439,7 +18842,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>391</v>
       </c>
@@ -18471,7 +18874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>392</v>
       </c>
@@ -18503,7 +18906,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>393</v>
       </c>
@@ -18535,7 +18938,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>394</v>
       </c>
@@ -18567,7 +18970,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>395</v>
       </c>
@@ -18599,7 +19002,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>396</v>
       </c>
@@ -18631,7 +19034,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>397</v>
       </c>
@@ -18663,7 +19066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>398</v>
       </c>
@@ -18695,7 +19098,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>399</v>
       </c>
@@ -18727,7 +19130,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>400</v>
       </c>
@@ -18759,7 +19162,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>401</v>
       </c>
@@ -18791,7 +19194,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>402</v>
       </c>
@@ -18823,7 +19226,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>403</v>
       </c>
@@ -18855,7 +19258,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>404</v>
       </c>
@@ -18887,7 +19290,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>405</v>
       </c>
@@ -18919,7 +19322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>406</v>
       </c>
@@ -18951,7 +19354,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>407</v>
       </c>
@@ -18983,7 +19386,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>408</v>
       </c>
@@ -19015,7 +19418,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>409</v>
       </c>
@@ -19047,7 +19450,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>410</v>
       </c>
@@ -19079,7 +19482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>411</v>
       </c>
@@ -19111,7 +19514,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>412</v>
       </c>
@@ -19143,7 +19546,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>413</v>
       </c>
@@ -19175,7 +19578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>414</v>
       </c>
@@ -19207,7 +19610,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>415</v>
       </c>
@@ -19239,7 +19642,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>416</v>
       </c>
@@ -19271,7 +19674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>417</v>
       </c>
@@ -19303,7 +19706,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>418</v>
       </c>
@@ -19335,7 +19738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>419</v>
       </c>
@@ -19367,7 +19770,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>420</v>
       </c>
@@ -19399,7 +19802,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>421</v>
       </c>
@@ -19431,7 +19834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>422</v>
       </c>
@@ -19463,7 +19866,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>423</v>
       </c>
@@ -19495,7 +19898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>424</v>
       </c>
@@ -19527,7 +19930,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>425</v>
       </c>
@@ -19559,7 +19962,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>426</v>
       </c>
@@ -19591,7 +19994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>427</v>
       </c>
@@ -19623,7 +20026,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>428</v>
       </c>
@@ -19655,7 +20058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>429</v>
       </c>
@@ -19687,7 +20090,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>430</v>
       </c>
@@ -19719,7 +20122,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>431</v>
       </c>
@@ -19751,7 +20154,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>432</v>
       </c>
@@ -19783,7 +20186,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>433</v>
       </c>
@@ -19815,7 +20218,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>434</v>
       </c>
@@ -19847,7 +20250,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>435</v>
       </c>
@@ -19879,7 +20282,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>436</v>
       </c>
@@ -19911,7 +20314,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>437</v>
       </c>
@@ -19943,7 +20346,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>438</v>
       </c>
@@ -19975,7 +20378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>439</v>
       </c>
@@ -20007,7 +20410,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>440</v>
       </c>
@@ -20039,7 +20442,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>441</v>
       </c>
@@ -20071,7 +20474,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>442</v>
       </c>
@@ -20103,7 +20506,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>443</v>
       </c>
@@ -20135,7 +20538,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>444</v>
       </c>
@@ -20167,7 +20570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>445</v>
       </c>
@@ -20199,7 +20602,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>446</v>
       </c>
@@ -20231,7 +20634,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>447</v>
       </c>
@@ -20263,7 +20666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>448</v>
       </c>
@@ -20295,7 +20698,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>449</v>
       </c>
@@ -20327,7 +20730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>450</v>
       </c>
@@ -20359,7 +20762,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>451</v>
       </c>
@@ -20391,7 +20794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>452</v>
       </c>
@@ -20423,7 +20826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>453</v>
       </c>
@@ -20455,7 +20858,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>454</v>
       </c>
@@ -20487,7 +20890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>455</v>
       </c>
@@ -20519,7 +20922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>456</v>
       </c>
@@ -20551,7 +20954,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>457</v>
       </c>
@@ -20583,7 +20986,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>458</v>
       </c>
@@ -20615,7 +21018,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>459</v>
       </c>
@@ -20647,7 +21050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>460</v>
       </c>
@@ -20679,7 +21082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>461</v>
       </c>
@@ -20711,7 +21114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>462</v>
       </c>
@@ -20743,7 +21146,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>463</v>
       </c>
@@ -20775,7 +21178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>464</v>
       </c>
@@ -20807,7 +21210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>465</v>
       </c>
@@ -20839,7 +21242,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>466</v>
       </c>
@@ -20871,7 +21274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>467</v>
       </c>
@@ -20903,7 +21306,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>468</v>
       </c>
@@ -20935,7 +21338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>469</v>
       </c>
@@ -20967,7 +21370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>470</v>
       </c>
@@ -20999,7 +21402,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>471</v>
       </c>
@@ -21031,7 +21434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>472</v>
       </c>
@@ -21063,7 +21466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>473</v>
       </c>
@@ -21095,7 +21498,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>474</v>
       </c>
@@ -21127,7 +21530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>475</v>
       </c>
@@ -21159,7 +21562,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>476</v>
       </c>
@@ -21191,7 +21594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>477</v>
       </c>
@@ -21223,7 +21626,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>478</v>
       </c>
@@ -21255,7 +21658,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>479</v>
       </c>
@@ -21287,7 +21690,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>480</v>
       </c>
@@ -21319,7 +21722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>481</v>
       </c>
@@ -21351,7 +21754,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>482</v>
       </c>
@@ -21383,7 +21786,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>483</v>
       </c>
@@ -21415,7 +21818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>484</v>
       </c>
@@ -21447,7 +21850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>485</v>
       </c>
@@ -21479,7 +21882,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>486</v>
       </c>
@@ -21511,7 +21914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>487</v>
       </c>
@@ -21543,7 +21946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>488</v>
       </c>
@@ -21586,14 +21989,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.9140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>626</v>
       </c>
@@ -21604,7 +22007,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -21615,7 +22018,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>627</v>
       </c>
@@ -21626,7 +22029,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>630</v>
       </c>
@@ -21637,7 +22040,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>633</v>
       </c>
@@ -21648,7 +22051,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>635</v>
       </c>
@@ -21659,7 +22062,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>637</v>
       </c>
@@ -21670,7 +22073,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>639</v>
       </c>
@@ -21681,7 +22084,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>640</v>
       </c>
@@ -21692,7 +22095,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>627</v>
       </c>
@@ -21703,7 +22106,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>643</v>
       </c>
@@ -21714,7 +22117,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>635</v>
       </c>
@@ -21725,7 +22128,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>645</v>
       </c>
@@ -21736,7 +22139,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>646</v>
       </c>
@@ -21747,7 +22150,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>627</v>
       </c>
@@ -21758,7 +22161,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>649</v>
       </c>
@@ -21769,11 +22172,11 @@
         <v>632</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>635</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>650</v>
       </c>
       <c r="C19" t="s">
@@ -21801,7 +22204,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C4 A6:C19 A5 C5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C4 A6:C18 A5 C5 A19 C19" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -21809,9 +22212,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>651</v>
       </c>
@@ -21846,7 +22249,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>660</v>
       </c>
@@ -21881,7 +22284,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>210</v>
       </c>
@@ -21916,7 +22319,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>154</v>
       </c>
@@ -21962,12 +22365,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>678</v>
       </c>
@@ -21978,7 +22381,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>681</v>
       </c>
@@ -21989,7 +22392,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>683</v>
       </c>
@@ -22000,7 +22403,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>685</v>
       </c>
@@ -22011,7 +22414,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>687</v>
       </c>
@@ -22022,15 +22425,15 @@
         <v>689</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>690</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>691</v>
       </c>
@@ -22041,7 +22444,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>692</v>
       </c>
@@ -22052,7 +22455,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>693</v>
       </c>
@@ -22063,7 +22466,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>694</v>
       </c>
@@ -22076,7 +22479,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{6794E79B-E8D6-4D28-8342-139A5ED5576A}"/>
+    <hyperlink ref="B6" r:id="rId1" display="keerthi@quantarra.io" xr:uid="{6794E79B-E8D6-4D28-8342-139A5ED5576A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D688307FDBA934CE52A31ED8FB17F8A4534B0E35" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F6E263-7F90-46D0-BDB3-D8E14121EC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regression" sheetId="1" r:id="rId1"/>

--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5770" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5781" uniqueCount="749">
   <si>
     <t>Test case</t>
   </si>
@@ -2198,6 +2198,24 @@
   </si>
   <si>
     <t>TG-1 to TG-7 (all)</t>
+  </si>
+  <si>
+    <t>PRJAT-1260</t>
+  </si>
+  <si>
+    <t>[QA] Internal Audit tab: filter button does not show active-filter count badge</t>
+  </si>
+  <si>
+    <t>qa-block, staging</t>
+  </si>
+  <si>
+    <t>To Do</t>
+  </si>
+  <si>
+    <t>TG-7 Scenario 7 TC-11b</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
   </si>
   <si>
     <t>Setting</t>
@@ -2684,7 +2702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3160,7 +3178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -3333,7 +3351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -3833,7 +3851,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" ht="14.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>109</v>
       </c>
@@ -22621,7 +22639,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
@@ -22770,6 +22788,41 @@
         <v>18</v>
       </c>
       <c r="K4" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>725</v>
+      </c>
+      <c r="B5" t="s">
+        <v>726</v>
+      </c>
+      <c r="C5" t="s">
+        <v>709</v>
+      </c>
+      <c r="D5" t="s">
+        <v>710</v>
+      </c>
+      <c r="E5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" t="s">
+        <v>727</v>
+      </c>
+      <c r="H5" t="s">
+        <v>728</v>
+      </c>
+      <c r="I5" t="s">
+        <v>729</v>
+      </c>
+      <c r="J5" t="s">
+        <v>730</v>
+      </c>
+      <c r="K5" t="s">
         <v>716</v>
       </c>
     </row>
@@ -22789,70 +22842,70 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="B1" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="C1" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="B5" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C5" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="B7" t="s">
         <v>155</v>
@@ -22863,7 +22916,7 @@
     </row>
     <row r="8" ht="15.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="B8" t="s">
         <v>155</v>
@@ -22874,7 +22927,7 @@
     </row>
     <row r="9" ht="15.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B9" t="s">
         <v>155</v>
@@ -22885,7 +22938,7 @@
     </row>
     <row r="10" ht="15.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="B10" t="s">
         <v>155</v>

--- a/Automation/tests/New_Testcase.xlsx
+++ b/Automation/tests/New_Testcase.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E09D09-DBEE-4183-8A25-B1938F74766E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="732" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Regression" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="E2E Flow" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Console Errors" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="API Test Cases" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Test data" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Jira Tracker" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Configuration" state="visible" r:id="rId10"/>
+    <sheet name="Regression" sheetId="1" r:id="rId1"/>
+    <sheet name="E2E Flow" sheetId="2" r:id="rId2"/>
+    <sheet name="Console Errors" sheetId="3" r:id="rId3"/>
+    <sheet name="API Test Cases" sheetId="4" r:id="rId4"/>
+    <sheet name="Test data" sheetId="5" r:id="rId5"/>
+    <sheet name="Jira Tracker" sheetId="6" r:id="rId6"/>
+    <sheet name="Configuration" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Regression!$A$2:$J$2</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5781" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5781" uniqueCount="748">
   <si>
     <t>Test case</t>
   </si>
@@ -2255,9 +2256,6 @@
   </si>
   <si>
     <t>Email Recipients</t>
-  </si>
-  <si>
-    <t>keerthi@quantarra.io, deepak@quantarra.io</t>
   </si>
   <si>
     <t>Notes:</t>
@@ -2275,22 +2273,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="12"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="12"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2310,14 +2316,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2654,9 +2663,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J91"/>
-  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="92" customWidth="1"/>
@@ -2702,7 +2711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2803,7 +2812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2988,7 +2997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -2999,7 +3008,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3132,7 +3141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -3155,7 +3164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -3178,7 +3187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -3244,7 +3253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -3270,7 +3279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -3299,7 +3308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -3325,7 +3334,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -3351,7 +3360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -3359,7 +3368,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -3388,7 +3397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -3417,7 +3426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -3446,7 +3455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -3475,7 +3484,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -3501,7 +3510,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>43</v>
       </c>
@@ -3527,7 +3536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>56</v>
       </c>
@@ -3553,7 +3562,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -3582,7 +3591,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>86</v>
       </c>
@@ -3608,7 +3617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>88</v>
       </c>
@@ -3634,7 +3643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>90</v>
       </c>
@@ -3663,7 +3672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>93</v>
       </c>
@@ -3689,7 +3698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -3715,7 +3724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>97</v>
       </c>
@@ -3741,7 +3750,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>99</v>
       </c>
@@ -3767,7 +3776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>101</v>
       </c>
@@ -3793,7 +3802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>103</v>
       </c>
@@ -3822,7 +3831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>106</v>
       </c>
@@ -3851,7 +3860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>109</v>
       </c>
@@ -3859,7 +3868,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="48" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -3885,7 +3894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -3914,7 +3923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -3943,7 +3952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -3972,7 +3981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>40</v>
       </c>
@@ -4001,7 +4010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>43</v>
       </c>
@@ -4027,7 +4036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -4053,7 +4062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -4079,7 +4088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -4105,7 +4114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -4131,7 +4140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>90</v>
       </c>
@@ -4157,7 +4166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -4186,7 +4195,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -4215,7 +4224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>97</v>
       </c>
@@ -4244,7 +4253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>99</v>
       </c>
@@ -4270,7 +4279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>101</v>
       </c>
@@ -4296,7 +4305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>103</v>
       </c>
@@ -4322,7 +4331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>106</v>
       </c>
@@ -4351,7 +4360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>137</v>
       </c>
@@ -4380,7 +4389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" ht="14.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -4403,7 +4412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" ht="14.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -4426,7 +4435,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" ht="14.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>144</v>
       </c>
@@ -4449,7 +4458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" ht="14.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>146</v>
       </c>
@@ -4472,7 +4481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" ht="14.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>148</v>
       </c>
@@ -4498,7 +4507,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" ht="14.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>151</v>
       </c>
@@ -4521,7 +4530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>153</v>
       </c>
@@ -4553,7 +4562,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -4585,7 +4594,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -4617,7 +4626,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="76" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>24</v>
       </c>
@@ -4649,7 +4658,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>37</v>
       </c>
@@ -4681,7 +4690,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="78" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -4713,7 +4722,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>43</v>
       </c>
@@ -4745,7 +4754,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="80" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>56</v>
       </c>
@@ -4777,7 +4786,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="81" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -4809,7 +4818,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="82" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -4841,7 +4850,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="83" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>88</v>
       </c>
@@ -4873,7 +4882,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="84" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>90</v>
       </c>
@@ -4905,7 +4914,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="85" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -4937,7 +4946,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="86" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>95</v>
       </c>
@@ -4969,7 +4978,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="87" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>97</v>
       </c>
@@ -5001,7 +5010,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="88" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -5033,7 +5042,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="89" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -5065,7 +5074,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="90" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>103</v>
       </c>
@@ -5097,7 +5106,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="91" ht="14.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>106</v>
       </c>
@@ -5135,9 +5144,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
     <col min="2" max="2" width="99.54296875" customWidth="1"/>
@@ -5170,7 +5179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>197</v>
       </c>
@@ -5413,7 +5422,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -5436,7 +5445,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -5459,7 +5468,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -5482,7 +5491,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="17" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -5568,7 +5577,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>216</v>
       </c>
@@ -5619,7 +5628,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="24" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -5639,7 +5648,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -5662,7 +5671,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="26" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -5685,7 +5694,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="27" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -5708,7 +5717,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="28" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -5731,7 +5740,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="29" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>83</v>
       </c>
@@ -5754,7 +5763,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="30" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>86</v>
       </c>
@@ -5777,7 +5786,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="31" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -5800,7 +5809,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="32" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -5823,7 +5832,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="33" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>93</v>
       </c>
@@ -5846,7 +5855,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="34" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>95</v>
       </c>
@@ -5869,7 +5878,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="35" ht="15.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>97</v>
       </c>
@@ -5892,22 +5901,22 @@
         <v>242</v>
       </c>
     </row>
-    <row r="36" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="37" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="38" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="39" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>106</v>
       </c>
@@ -5918,9 +5927,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -6520,7 +6529,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>283</v>
       </c>
@@ -6546,7 +6555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>284</v>
       </c>
@@ -6572,7 +6581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>285</v>
       </c>
@@ -6598,7 +6607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>286</v>
       </c>
@@ -6624,7 +6633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>287</v>
       </c>
@@ -6650,7 +6659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>288</v>
       </c>
@@ -6676,7 +6685,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>289</v>
       </c>
@@ -6702,7 +6711,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>290</v>
       </c>
@@ -6728,7 +6737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" ht="15.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>291</v>
       </c>
@@ -6760,9 +6769,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J489"/>
-  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -6796,7 +6805,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -6828,7 +6837,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -6860,7 +6869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -6892,7 +6901,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6924,7 +6933,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6956,7 +6965,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6988,7 +6997,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="8" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7020,7 +7029,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7052,7 +7061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7084,7 +7093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7116,7 +7125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7148,7 +7157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7180,7 +7189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7212,7 +7221,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -7244,7 +7253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7276,7 +7285,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="17" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -7308,7 +7317,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -7340,7 +7349,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -7372,7 +7381,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -7404,7 +7413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -7436,7 +7445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -7468,7 +7477,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="23" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -7500,7 +7509,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -7532,7 +7541,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="25" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -7564,7 +7573,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="26" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -7596,7 +7605,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -7628,7 +7637,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="28" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -7660,7 +7669,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -7692,7 +7701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -7724,7 +7733,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -7756,7 +7765,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="32" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -7788,7 +7797,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -7820,7 +7829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -7852,7 +7861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -7884,7 +7893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -7916,7 +7925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7948,7 +7957,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7980,7 +7989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8012,7 +8021,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8044,7 +8053,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8076,7 +8085,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="42" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8108,7 +8117,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="43" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8140,7 +8149,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8172,7 +8181,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="45" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8204,7 +8213,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8236,7 +8245,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8268,7 +8277,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8300,7 +8309,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="49" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8332,7 +8341,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="50" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8364,7 +8373,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8396,7 +8405,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8428,7 +8437,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8460,7 +8469,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8492,7 +8501,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8524,7 +8533,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="56" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8556,7 +8565,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8588,7 +8597,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="58" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8620,7 +8629,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="59" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8652,7 +8661,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="60" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8684,7 +8693,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="61" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -8716,7 +8725,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="62" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -8748,7 +8757,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -8780,7 +8789,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="64" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -8812,7 +8821,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="65" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -8844,7 +8853,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="66" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -8876,7 +8885,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="67" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -8908,7 +8917,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="68" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -8940,7 +8949,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="69" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -8972,7 +8981,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="70" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9004,7 +9013,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="71" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9036,7 +9045,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="72" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9068,7 +9077,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="73" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9100,7 +9109,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="74" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9132,7 +9141,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9164,7 +9173,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="76" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9196,7 +9205,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9228,7 +9237,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="78" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9260,7 +9269,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9292,7 +9301,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9324,7 +9333,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="81" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9356,7 +9365,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="82" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -9388,7 +9397,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="83" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9420,7 +9429,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="84" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9452,7 +9461,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9484,7 +9493,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="86" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9516,7 +9525,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="87" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9548,7 +9557,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="88" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9580,7 +9589,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="89" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -9612,7 +9621,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -9644,7 +9653,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="91" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -9676,7 +9685,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="92" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -9708,7 +9717,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="93" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -9740,7 +9749,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -9772,7 +9781,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -9804,7 +9813,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="96" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -9836,7 +9845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -9868,7 +9877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -9900,7 +9909,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="99" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -9932,7 +9941,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="100" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -9964,7 +9973,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="101" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -9996,7 +10005,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="102" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -10028,7 +10037,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="103" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -10060,7 +10069,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="104" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10092,7 +10101,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="105" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10124,7 +10133,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="106" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10156,7 +10165,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="107" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10188,7 +10197,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="108" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10220,7 +10229,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="109" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10252,7 +10261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10284,7 +10293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -10316,7 +10325,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="112" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -10348,7 +10357,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="113" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -10380,7 +10389,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="114" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -10412,7 +10421,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="115" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -10444,7 +10453,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="116" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -10476,7 +10485,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="117" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -10508,7 +10517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -10540,7 +10549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -10572,7 +10581,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="120" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -10604,7 +10613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -10636,7 +10645,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -10668,7 +10677,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="123" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -10700,7 +10709,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="124" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -10732,7 +10741,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="125" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -10764,7 +10773,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="126" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -10796,7 +10805,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="127" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -10828,7 +10837,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="128" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -10860,7 +10869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -10892,7 +10901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -10924,7 +10933,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="131" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -10956,7 +10965,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="132" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -10988,7 +10997,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="133" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -11020,7 +11029,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="134" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -11052,7 +11061,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="135" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -11084,7 +11093,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="136" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -11116,7 +11125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -11148,7 +11157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -11180,7 +11189,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="139" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -11212,7 +11221,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="140" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -11244,7 +11253,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="141" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -11276,7 +11285,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="142" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -11308,7 +11317,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="143" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -11340,7 +11349,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="144" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -11372,7 +11381,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="145" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -11404,7 +11413,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="146" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -11436,7 +11445,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="147" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -11468,7 +11477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -11500,7 +11509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -11532,7 +11541,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="150" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -11564,7 +11573,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="151" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -11596,7 +11605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -11628,7 +11637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -11660,7 +11669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -11692,7 +11701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="155" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -11724,7 +11733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -11756,7 +11765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -11788,7 +11797,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="158" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -11820,7 +11829,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="159" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -11852,7 +11861,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="160" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -11884,7 +11893,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="161" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -11916,7 +11925,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="162" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>161</v>
       </c>
@@ -11948,7 +11957,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="163" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>162</v>
       </c>
@@ -11980,7 +11989,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="164" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>163</v>
       </c>
@@ -12012,7 +12021,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="165" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>164</v>
       </c>
@@ -12044,7 +12053,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="166" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>165</v>
       </c>
@@ -12076,7 +12085,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="167" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>166</v>
       </c>
@@ -12108,7 +12117,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="168" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>167</v>
       </c>
@@ -12140,7 +12149,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="169" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>168</v>
       </c>
@@ -12172,7 +12181,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="170" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>169</v>
       </c>
@@ -12204,7 +12213,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="171" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>170</v>
       </c>
@@ -12236,7 +12245,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="172" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>171</v>
       </c>
@@ -12268,7 +12277,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="173" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>172</v>
       </c>
@@ -12300,7 +12309,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="174" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>173</v>
       </c>
@@ -12332,7 +12341,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="175" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>174</v>
       </c>
@@ -12364,7 +12373,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="176" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>175</v>
       </c>
@@ -12396,7 +12405,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="177" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>176</v>
       </c>
@@ -12428,7 +12437,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="178" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>177</v>
       </c>
@@ -12460,7 +12469,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="179" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>178</v>
       </c>
@@ -12492,7 +12501,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="180" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>179</v>
       </c>
@@ -12524,7 +12533,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="181" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>180</v>
       </c>
@@ -12556,7 +12565,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="182" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>181</v>
       </c>
@@ -12588,7 +12597,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="183" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>182</v>
       </c>
@@ -12620,7 +12629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>183</v>
       </c>
@@ -12652,7 +12661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>184</v>
       </c>
@@ -12684,7 +12693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>185</v>
       </c>
@@ -12716,7 +12725,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="187" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>186</v>
       </c>
@@ -12748,7 +12757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>187</v>
       </c>
@@ -12780,7 +12789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>188</v>
       </c>
@@ -12812,7 +12821,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="190" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>189</v>
       </c>
@@ -12844,7 +12853,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="191" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>190</v>
       </c>
@@ -12876,7 +12885,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="192" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>191</v>
       </c>
@@ -12908,7 +12917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>192</v>
       </c>
@@ -12940,7 +12949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>193</v>
       </c>
@@ -12972,7 +12981,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="195" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>194</v>
       </c>
@@ -13004,7 +13013,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="196" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>195</v>
       </c>
@@ -13036,7 +13045,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="197" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>196</v>
       </c>
@@ -13068,7 +13077,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="198" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>197</v>
       </c>
@@ -13100,7 +13109,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="199" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>198</v>
       </c>
@@ -13132,7 +13141,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="200" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>199</v>
       </c>
@@ -13164,7 +13173,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="201" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>200</v>
       </c>
@@ -13196,7 +13205,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="202" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>201</v>
       </c>
@@ -13228,7 +13237,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="203" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>202</v>
       </c>
@@ -13260,7 +13269,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="204" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>203</v>
       </c>
@@ -13292,7 +13301,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="205" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>204</v>
       </c>
@@ -13324,7 +13333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>205</v>
       </c>
@@ -13356,7 +13365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>206</v>
       </c>
@@ -13388,7 +13397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>207</v>
       </c>
@@ -13420,7 +13429,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="209" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>208</v>
       </c>
@@ -13452,7 +13461,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="210" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>209</v>
       </c>
@@ -13484,7 +13493,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="211" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>210</v>
       </c>
@@ -13516,7 +13525,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="212" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>211</v>
       </c>
@@ -13548,7 +13557,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="213" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>212</v>
       </c>
@@ -13580,7 +13589,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="214" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>213</v>
       </c>
@@ -13612,7 +13621,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="215" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>214</v>
       </c>
@@ -13644,7 +13653,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="216" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>215</v>
       </c>
@@ -13676,7 +13685,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="217" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>216</v>
       </c>
@@ -13708,7 +13717,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="218" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>217</v>
       </c>
@@ -13740,7 +13749,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="219" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>218</v>
       </c>
@@ -13772,7 +13781,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="220" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>219</v>
       </c>
@@ -13804,7 +13813,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="221" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>220</v>
       </c>
@@ -13836,7 +13845,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="222" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>221</v>
       </c>
@@ -13868,7 +13877,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="223" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>222</v>
       </c>
@@ -13900,7 +13909,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>223</v>
       </c>
@@ -13932,7 +13941,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="225" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>224</v>
       </c>
@@ -13964,7 +13973,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="226" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>225</v>
       </c>
@@ -13996,7 +14005,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="227" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>226</v>
       </c>
@@ -14028,7 +14037,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="228" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>227</v>
       </c>
@@ -14060,7 +14069,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>228</v>
       </c>
@@ -14092,7 +14101,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="230" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>229</v>
       </c>
@@ -14124,7 +14133,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="231" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>230</v>
       </c>
@@ -14156,7 +14165,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="232" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>231</v>
       </c>
@@ -14188,7 +14197,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="233" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>232</v>
       </c>
@@ -14220,7 +14229,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="234" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>233</v>
       </c>
@@ -14252,7 +14261,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="235" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>234</v>
       </c>
@@ -14284,7 +14293,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="236" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>235</v>
       </c>
@@ -14316,7 +14325,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="237" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>236</v>
       </c>
@@ -14348,7 +14357,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>237</v>
       </c>
@@ -14380,7 +14389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>238</v>
       </c>
@@ -14412,7 +14421,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>239</v>
       </c>
@@ -14444,7 +14453,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="241" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>240</v>
       </c>
@@ -14476,7 +14485,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="242" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>241</v>
       </c>
@@ -14508,7 +14517,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="243" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>242</v>
       </c>
@@ -14540,7 +14549,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="244" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>243</v>
       </c>
@@ -14572,7 +14581,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="245" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>244</v>
       </c>
@@ -14604,7 +14613,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="246" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>245</v>
       </c>
@@ -14636,7 +14645,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="247" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>246</v>
       </c>
@@ -14668,7 +14677,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="248" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>247</v>
       </c>
@@ -14700,7 +14709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="249" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>248</v>
       </c>
@@ -14732,7 +14741,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="250" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>249</v>
       </c>
@@ -14764,7 +14773,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="251" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>250</v>
       </c>
@@ -14796,7 +14805,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="252" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>251</v>
       </c>
@@ -14828,7 +14837,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="253" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>252</v>
       </c>
@@ -14860,7 +14869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>253</v>
       </c>
@@ -14892,7 +14901,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="255" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>254</v>
       </c>
@@ -14924,7 +14933,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="256" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>255</v>
       </c>
@@ -14956,7 +14965,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="257" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>256</v>
       </c>
@@ -14988,7 +14997,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="258" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>257</v>
       </c>
@@ -15020,7 +15029,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>258</v>
       </c>
@@ -15052,7 +15061,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="260" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>259</v>
       </c>
@@ -15084,7 +15093,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="261" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>260</v>
       </c>
@@ -15116,7 +15125,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="262" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>261</v>
       </c>
@@ -15148,7 +15157,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="263" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>262</v>
       </c>
@@ -15180,7 +15189,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="264" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>263</v>
       </c>
@@ -15212,7 +15221,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="265" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>264</v>
       </c>
@@ -15244,7 +15253,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="266" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>265</v>
       </c>
@@ -15276,7 +15285,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="267" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>266</v>
       </c>
@@ -15308,7 +15317,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="268" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>267</v>
       </c>
@@ -15340,7 +15349,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="269" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>268</v>
       </c>
@@ -15372,7 +15381,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="270" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>269</v>
       </c>
@@ -15404,7 +15413,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="271" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>270</v>
       </c>
@@ -15436,7 +15445,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="272" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>271</v>
       </c>
@@ -15468,7 +15477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>272</v>
       </c>
@@ -15500,7 +15509,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="274" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>273</v>
       </c>
@@ -15532,7 +15541,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="275" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>274</v>
       </c>
@@ -15564,7 +15573,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="276" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>275</v>
       </c>
@@ -15596,7 +15605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>276</v>
       </c>
@@ -15628,7 +15637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>277</v>
       </c>
@@ -15660,7 +15669,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="279" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>278</v>
       </c>
@@ -15692,7 +15701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="280" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>279</v>
       </c>
@@ -15724,7 +15733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>280</v>
       </c>
@@ -15756,7 +15765,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="282" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>281</v>
       </c>
@@ -15788,7 +15797,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="283" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>282</v>
       </c>
@@ -15820,7 +15829,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="284" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>283</v>
       </c>
@@ -15852,7 +15861,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="285" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>284</v>
       </c>
@@ -15884,7 +15893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>285</v>
       </c>
@@ -15916,7 +15925,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="287" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>286</v>
       </c>
@@ -15948,7 +15957,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="288" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>287</v>
       </c>
@@ -15980,7 +15989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>288</v>
       </c>
@@ -16012,7 +16021,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="290" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>289</v>
       </c>
@@ -16044,7 +16053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>290</v>
       </c>
@@ -16076,7 +16085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="292" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>291</v>
       </c>
@@ -16108,7 +16117,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>292</v>
       </c>
@@ -16140,7 +16149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>293</v>
       </c>
@@ -16172,7 +16181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>294</v>
       </c>
@@ -16204,7 +16213,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="296" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>295</v>
       </c>
@@ -16236,7 +16245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>296</v>
       </c>
@@ -16268,7 +16277,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="298" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>297</v>
       </c>
@@ -16300,7 +16309,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="299" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>298</v>
       </c>
@@ -16332,7 +16341,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="300" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>299</v>
       </c>
@@ -16364,7 +16373,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>300</v>
       </c>
@@ -16396,7 +16405,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="302" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>301</v>
       </c>
@@ -16428,7 +16437,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>302</v>
       </c>
@@ -16460,7 +16469,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="304" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>303</v>
       </c>
@@ -16492,7 +16501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>304</v>
       </c>
@@ -16524,7 +16533,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="306" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>305</v>
       </c>
@@ -16556,7 +16565,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="307" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>306</v>
       </c>
@@ -16588,7 +16597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="308" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>307</v>
       </c>
@@ -16620,7 +16629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>308</v>
       </c>
@@ -16652,7 +16661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="310" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>309</v>
       </c>
@@ -16684,7 +16693,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="311" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>310</v>
       </c>
@@ -16716,7 +16725,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>311</v>
       </c>
@@ -16748,7 +16757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="313" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>312</v>
       </c>
@@ -16780,7 +16789,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="314" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>313</v>
       </c>
@@ -16812,7 +16821,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="315" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>314</v>
       </c>
@@ -16844,7 +16853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>315</v>
       </c>
@@ -16876,7 +16885,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="317" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>316</v>
       </c>
@@ -16908,7 +16917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="318" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>317</v>
       </c>
@@ -16940,7 +16949,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="319" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>318</v>
       </c>
@@ -16972,7 +16981,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="320" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>319</v>
       </c>
@@ -17004,7 +17013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="321" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>320</v>
       </c>
@@ -17036,7 +17045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>321</v>
       </c>
@@ -17068,7 +17077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="323" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>322</v>
       </c>
@@ -17100,7 +17109,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="324" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>323</v>
       </c>
@@ -17132,7 +17141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="325" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>324</v>
       </c>
@@ -17164,7 +17173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="326" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>325</v>
       </c>
@@ -17196,7 +17205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="327" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>326</v>
       </c>
@@ -17228,7 +17237,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="328" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>327</v>
       </c>
@@ -17260,7 +17269,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="329" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>328</v>
       </c>
@@ -17292,7 +17301,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="330" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>329</v>
       </c>
@@ -17324,7 +17333,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="331" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>330</v>
       </c>
@@ -17356,7 +17365,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="332" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>331</v>
       </c>
@@ -17388,7 +17397,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="333" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>332</v>
       </c>
@@ -17420,7 +17429,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="334" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>333</v>
       </c>
@@ -17452,7 +17461,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="335" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>334</v>
       </c>
@@ -17484,7 +17493,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="336" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>335</v>
       </c>
@@ -17516,7 +17525,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="337" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>336</v>
       </c>
@@ -17548,7 +17557,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="338" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>337</v>
       </c>
@@ -17580,7 +17589,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="339" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>338</v>
       </c>
@@ -17612,7 +17621,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="340" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>339</v>
       </c>
@@ -17644,7 +17653,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="341" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>340</v>
       </c>
@@ -17676,7 +17685,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="342" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>341</v>
       </c>
@@ -17708,7 +17717,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="343" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>342</v>
       </c>
@@ -17740,7 +17749,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="344" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>343</v>
       </c>
@@ -17772,7 +17781,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="345" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>344</v>
       </c>
@@ -17804,7 +17813,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="346" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>345</v>
       </c>
@@ -17836,7 +17845,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="347" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>346</v>
       </c>
@@ -17868,7 +17877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="348" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>347</v>
       </c>
@@ -17900,7 +17909,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="349" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>348</v>
       </c>
@@ -17932,7 +17941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="350" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>349</v>
       </c>
@@ -17964,7 +17973,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="351" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>350</v>
       </c>
@@ -17996,7 +18005,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="352" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>351</v>
       </c>
@@ -18028,7 +18037,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="353" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>352</v>
       </c>
@@ -18060,7 +18069,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="354" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>353</v>
       </c>
@@ -18092,7 +18101,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="355" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>354</v>
       </c>
@@ -18124,7 +18133,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="356" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>355</v>
       </c>
@@ -18156,7 +18165,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="357" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>356</v>
       </c>
@@ -18188,7 +18197,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="358" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>357</v>
       </c>
@@ -18220,7 +18229,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="359" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>358</v>
       </c>
@@ -18252,7 +18261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="360" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>359</v>
       </c>
@@ -18284,7 +18293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="361" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>360</v>
       </c>
@@ -18316,7 +18325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="362" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>361</v>
       </c>
@@ -18348,7 +18357,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>362</v>
       </c>
@@ -18380,7 +18389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>363</v>
       </c>
@@ -18412,7 +18421,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="365" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>364</v>
       </c>
@@ -18444,7 +18453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="366" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>365</v>
       </c>
@@ -18476,7 +18485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="367" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>366</v>
       </c>
@@ -18508,7 +18517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="368" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>367</v>
       </c>
@@ -18540,7 +18549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="369" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>368</v>
       </c>
@@ -18572,7 +18581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>369</v>
       </c>
@@ -18604,7 +18613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>370</v>
       </c>
@@ -18636,7 +18645,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="372" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>371</v>
       </c>
@@ -18668,7 +18677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="373" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>372</v>
       </c>
@@ -18700,7 +18709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="374" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>373</v>
       </c>
@@ -18732,7 +18741,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="375" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>374</v>
       </c>
@@ -18764,7 +18773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>375</v>
       </c>
@@ -18796,7 +18805,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="377" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>376</v>
       </c>
@@ -18828,7 +18837,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="378" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>377</v>
       </c>
@@ -18860,7 +18869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="379" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>378</v>
       </c>
@@ -18892,7 +18901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="380" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>379</v>
       </c>
@@ -18924,7 +18933,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="381" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>380</v>
       </c>
@@ -18956,7 +18965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="382" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>381</v>
       </c>
@@ -18988,7 +18997,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="383" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>382</v>
       </c>
@@ -19020,7 +19029,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="384" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>383</v>
       </c>
@@ -19052,7 +19061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>384</v>
       </c>
@@ -19084,7 +19093,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="386" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>385</v>
       </c>
@@ -19116,7 +19125,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="387" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>386</v>
       </c>
@@ -19148,7 +19157,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="388" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>387</v>
       </c>
@@ -19180,7 +19189,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="389" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>388</v>
       </c>
@@ -19212,7 +19221,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="390" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>389</v>
       </c>
@@ -19244,7 +19253,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="391" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>390</v>
       </c>
@@ -19276,7 +19285,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="392" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>391</v>
       </c>
@@ -19308,7 +19317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="393" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>392</v>
       </c>
@@ -19340,7 +19349,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="394" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>393</v>
       </c>
@@ -19372,7 +19381,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="395" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>394</v>
       </c>
@@ -19404,7 +19413,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="396" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>395</v>
       </c>
@@ -19436,7 +19445,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="397" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>396</v>
       </c>
@@ -19468,7 +19477,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="398" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>397</v>
       </c>
@@ -19500,7 +19509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="399" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>398</v>
       </c>
@@ -19532,7 +19541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="400" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>399</v>
       </c>
@@ -19564,7 +19573,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="401" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>400</v>
       </c>
@@ -19596,7 +19605,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="402" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>401</v>
       </c>
@@ -19628,7 +19637,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="403" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>402</v>
       </c>
@@ -19660,7 +19669,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="404" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>403</v>
       </c>
@@ -19692,7 +19701,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="405" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>404</v>
       </c>
@@ -19724,7 +19733,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="406" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>405</v>
       </c>
@@ -19756,7 +19765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="407" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>406</v>
       </c>
@@ -19788,7 +19797,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="408" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>407</v>
       </c>
@@ -19820,7 +19829,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="409" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>408</v>
       </c>
@@ -19852,7 +19861,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="410" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>409</v>
       </c>
@@ -19884,7 +19893,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="411" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>410</v>
       </c>
@@ -19916,7 +19925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="412" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>411</v>
       </c>
@@ -19948,7 +19957,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="413" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>412</v>
       </c>
@@ -19980,7 +19989,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="414" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>413</v>
       </c>
@@ -20012,7 +20021,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="415" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>414</v>
       </c>
@@ -20044,7 +20053,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="416" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>415</v>
       </c>
@@ -20076,7 +20085,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="417" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417">
         <v>416</v>
       </c>
@@ -20108,7 +20117,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418">
         <v>417</v>
       </c>
@@ -20140,7 +20149,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="419" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419">
         <v>418</v>
       </c>
@@ -20172,7 +20181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="420" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420">
         <v>419</v>
       </c>
@@ -20204,7 +20213,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="421" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421">
         <v>420</v>
       </c>
@@ -20236,7 +20245,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="422" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422">
         <v>421</v>
       </c>
@@ -20268,7 +20277,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="423" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423">
         <v>422</v>
       </c>
@@ -20300,7 +20309,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="424" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424">
         <v>423</v>
       </c>
@@ -20332,7 +20341,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="425" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425">
         <v>424</v>
       </c>
@@ -20364,7 +20373,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="426" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426">
         <v>425</v>
       </c>
@@ -20396,7 +20405,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="427" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427">
         <v>426</v>
       </c>
@@ -20428,7 +20437,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428">
         <v>427</v>
       </c>
@@ -20460,7 +20469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="429" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429">
         <v>428</v>
       </c>
@@ -20492,7 +20501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="430" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430">
         <v>429</v>
       </c>
@@ -20524,7 +20533,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="431" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431">
         <v>430</v>
       </c>
@@ -20556,7 +20565,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="432" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432">
         <v>431</v>
       </c>
@@ -20588,7 +20597,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="433" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433">
         <v>432</v>
       </c>
@@ -20620,7 +20629,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="434" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434">
         <v>433</v>
       </c>
@@ -20652,7 +20661,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="435" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435">
         <v>434</v>
       </c>
@@ -20684,7 +20693,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="436" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436">
         <v>435</v>
       </c>
@@ -20716,7 +20725,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="437" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437">
         <v>436</v>
       </c>
@@ -20748,7 +20757,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="438" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438">
         <v>437</v>
       </c>
@@ -20780,7 +20789,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="439" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439">
         <v>438</v>
       </c>
@@ -20812,7 +20821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="440" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440">
         <v>439</v>
       </c>
@@ -20844,7 +20853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="441" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441">
         <v>440</v>
       </c>
@@ -20876,7 +20885,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="442" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442">
         <v>441</v>
       </c>
@@ -20908,7 +20917,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="443" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443">
         <v>442</v>
       </c>
@@ -20940,7 +20949,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="444" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444">
         <v>443</v>
       </c>
@@ -20972,7 +20981,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="445" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445">
         <v>444</v>
       </c>
@@ -21004,7 +21013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="446" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446">
         <v>445</v>
       </c>
@@ -21036,7 +21045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="447" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447">
         <v>446</v>
       </c>
@@ -21068,7 +21077,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="448" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448">
         <v>447</v>
       </c>
@@ -21100,7 +21109,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="449" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449">
         <v>448</v>
       </c>
@@ -21132,7 +21141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="450" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450">
         <v>449</v>
       </c>
@@ -21164,7 +21173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="451" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451">
         <v>450</v>
       </c>
@@ -21196,7 +21205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="452" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452">
         <v>451</v>
       </c>
@@ -21228,7 +21237,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="453" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453">
         <v>452</v>
       </c>
@@ -21260,7 +21269,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="454" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454">
         <v>453</v>
       </c>
@@ -21292,7 +21301,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="455" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455">
         <v>454</v>
       </c>
@@ -21324,7 +21333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="456" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456">
         <v>455</v>
       </c>
@@ -21356,7 +21365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457">
         <v>456</v>
       </c>
@@ -21388,7 +21397,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="458" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458">
         <v>457</v>
       </c>
@@ -21420,7 +21429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="459" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459">
         <v>458</v>
       </c>
@@ -21452,7 +21461,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="460" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460">
         <v>459</v>
       </c>
@@ -21484,7 +21493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="461" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461">
         <v>460</v>
       </c>
@@ -21516,7 +21525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="462" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462">
         <v>461</v>
       </c>
@@ -21548,7 +21557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="463" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463">
         <v>462</v>
       </c>
@@ -21580,7 +21589,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="464" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464">
         <v>463</v>
       </c>
@@ -21612,7 +21621,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="465" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465">
         <v>464</v>
       </c>
@@ -21644,7 +21653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466">
         <v>465</v>
       </c>
@@ -21676,7 +21685,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="467" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467">
         <v>466</v>
       </c>
@@ -21708,7 +21717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468">
         <v>467</v>
       </c>
@@ -21740,7 +21749,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="469" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469">
         <v>468</v>
       </c>
@@ -21772,7 +21781,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="470" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470">
         <v>469</v>
       </c>
@@ -21804,7 +21813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="471" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471">
         <v>470</v>
       </c>
@@ -21836,7 +21845,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="472" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472">
         <v>471</v>
       </c>
@@ -21868,7 +21877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="473" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473">
         <v>472</v>
       </c>
@@ -21900,7 +21909,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="474" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474">
         <v>473</v>
       </c>
@@ -21932,7 +21941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="475" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475">
         <v>474</v>
       </c>
@@ -21964,7 +21973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="476" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476">
         <v>475</v>
       </c>
@@ -21996,7 +22005,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="477" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477">
         <v>476</v>
       </c>
@@ -22028,7 +22037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="478" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478">
         <v>477</v>
       </c>
@@ -22060,7 +22069,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="479" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479">
         <v>478</v>
       </c>
@@ -22092,7 +22101,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="480" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480">
         <v>479</v>
       </c>
@@ -22124,7 +22133,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="481" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481">
         <v>480</v>
       </c>
@@ -22156,7 +22165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="482" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482">
         <v>481</v>
       </c>
@@ -22188,7 +22197,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="483" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483">
         <v>482</v>
       </c>
@@ -22220,7 +22229,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="484" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484">
         <v>483</v>
       </c>
@@ -22252,7 +22261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485">
         <v>484</v>
       </c>
@@ -22284,7 +22293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="486" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486">
         <v>485</v>
       </c>
@@ -22316,7 +22325,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="487" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487">
         <v>486</v>
       </c>
@@ -22348,7 +22357,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="488" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488">
         <v>487</v>
       </c>
@@ -22380,7 +22389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="489" ht="15.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489">
         <v>488</v>
       </c>
@@ -22418,9 +22427,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.90625" customWidth="1"/>
     <col min="2" max="2" width="34.6328125" customWidth="1"/>
@@ -22537,22 +22546,22 @@
         <v>676</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>690</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>691</v>
       </c>
       <c r="C12" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>682</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>681</v>
       </c>
       <c r="C13" t="s">
@@ -22616,31 +22625,31 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="B2" r:id="rId2"/>
-    <hyperlink ref="C2" r:id="rId3"/>
-    <hyperlink ref="B4" r:id="rId4"/>
-    <hyperlink ref="B5" r:id="rId5"/>
-    <hyperlink ref="B6" r:id="rId6"/>
-    <hyperlink ref="B7" r:id="rId7"/>
-    <hyperlink ref="A10" r:id="rId8"/>
-    <hyperlink ref="B10" r:id="rId9"/>
-    <hyperlink ref="C10" r:id="rId10"/>
-    <hyperlink ref="B12" r:id="rId11"/>
-    <hyperlink ref="B13" r:id="rId12"/>
-    <hyperlink ref="A16" r:id="rId13"/>
-    <hyperlink ref="B16" r:id="rId14"/>
-    <hyperlink ref="B18" r:id="rId15"/>
-    <hyperlink ref="B19" r:id="rId16"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="B7" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="A10" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="A16" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="B16" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="B18" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="B19" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.26953125" customWidth="1"/>
     <col min="2" max="2" width="60.6328125" customWidth="1"/>
@@ -22832,9 +22841,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.08984375" customWidth="1"/>
     <col min="3" max="3" width="42.36328125" customWidth="1"/>
@@ -22895,50 +22904,50 @@
         <v>742</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>743</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>744</v>
+      <c r="B6" s="2" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>744</v>
+      </c>
+      <c r="B7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>745</v>
       </c>
-      <c r="B7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="8" ht="15.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>746</v>
       </c>
-      <c r="B8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" ht="15.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>747</v>
-      </c>
-      <c r="B9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" ht="15.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>748</v>
       </c>
       <c r="B10" t="s">
         <v>155</v>
@@ -22949,7 +22958,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
